--- a/_docs_/trim02/03_estimación_costos/Aleyual_Gantt_Completo.xlsx
+++ b/_docs_/trim02/03_estimación_costos/Aleyual_Gantt_Completo.xlsx
@@ -328,7 +328,7 @@
     <t xml:space="preserve">4.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend React + JWT Auth</t>
+    <t xml:space="preserve">Frontend Blade + Sanctum Auth</t>
   </si>
   <si>
     <t xml:space="preserve">Aplicación Web</t>
@@ -349,7 +349,7 @@
     <t xml:space="preserve">5.1</t>
   </si>
   <si>
-    <t xml:space="preserve">API REST + JWT + CORS + Postman</t>
+    <t xml:space="preserve">API REST + Sanctum + CORS + Postman</t>
   </si>
   <si>
     <t xml:space="preserve">Documentación API</t>
@@ -640,7 +640,7 @@
     <t xml:space="preserve">quiero Iniciar sesión con usuario y contraseña segura</t>
   </si>
   <si>
-    <t xml:space="preserve">Login con credenciales / Token JWT / Redirección por rol</t>
+    <t xml:space="preserve">Login con credenciales / Token Sanctum / Redirección por rol</t>
   </si>
   <si>
     <t xml:space="preserve">Alta</t>
@@ -667,7 +667,7 @@
     <t xml:space="preserve">quiero Gestionar roles Admin, Vendedor y Domiciliario</t>
   </si>
   <si>
-    <t xml:space="preserve">Roles en BD / Permisos por módulo / Middleware JWT</t>
+    <t xml:space="preserve">Roles en BD / Permisos por módulo / Middleware Sanctum</t>
   </si>
   <si>
     <t xml:space="preserve">06 Nov 2026</t>
@@ -1195,7 +1195,7 @@
     <t xml:space="preserve">17 Ago – 09 Oct 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Prototipo navegable completo. Frontend base React + configuración JWT</t>
+    <t xml:space="preserve">Prototipo navegable completo. Frontend base Blade + configuración Sanctum</t>
   </si>
   <si>
     <t xml:space="preserve">T3-T4</t>
@@ -1408,7 +1408,7 @@
     <t xml:space="preserve">Seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">Rutas protegidas con JWT. Contraseñas con bcrypt. Sin datos sensibles expuestos en frontend.</t>
+    <t xml:space="preserve">Rutas protegidas con Sanctum. Contraseñas con bcrypt. Sin datos sensibles expuestos en frontend.</t>
   </si>
   <si>
     <t xml:space="preserve">Aceptación</t>
@@ -1576,7 +1576,7 @@
     <t xml:space="preserve">Procesamiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Compila React + corre servidor local de desarrollo simultáneamente sin lag</t>
+    <t xml:space="preserve">Compila assets + corre servidor local de desarrollo simultáneamente sin lag</t>
   </si>
   <si>
     <t xml:space="preserve">Crítico</t>
@@ -1603,7 +1603,7 @@
     <t xml:space="preserve">RAM</t>
   </si>
   <si>
-    <t xml:space="preserve">VS Code + Chrome + Postman + Node.js local corriendo a la vez sin swap</t>
+    <t xml:space="preserve">VS Code + Chrome + Postman + Laravel local corriendo a la vez sin swap</t>
   </si>
   <si>
     <t xml:space="preserve">SSD NVMe 1 TB</t>
@@ -1744,7 +1744,7 @@
     <t xml:space="preserve">Intel Core i5-12400 · 6C/12T · 2.5–4.4 GHz · 18 MB caché · Sin GPU</t>
   </si>
   <si>
-    <t xml:space="preserve">Sin GPU dedicada = menos calor y consumo. 6 núcleos manejan MySQL + Node.js + Nginx simultáneos 24/7</t>
+    <t xml:space="preserve">Sin GPU dedicada = menos calor y consumo. 6 núcleos manejan MySQL + PHP-FPM + Nginx simultáneos 24/7</t>
   </si>
   <si>
     <t xml:space="preserve">ASUS Prime B660M-A DDR4 · Micro-ATX · LGA1700 · 4 slots RAM</t>
@@ -1756,7 +1756,7 @@
     <t xml:space="preserve">32 GB DDR4 3200 MHz · Kingston Fury Beast · 2×16 GB</t>
   </si>
   <si>
-    <t xml:space="preserve">32 GB para MySQL + Node.js + Nginx + caché sin swap en horas pico de la tienda</t>
+    <t xml:space="preserve">32 GB para MySQL + PHP-FPM + Nginx + caché sin swap en horas pico de la tienda</t>
   </si>
   <si>
     <t xml:space="preserve">SSD NVMe 500 GB</t>
@@ -1768,7 +1768,7 @@
     <t xml:space="preserve">Sistema OS</t>
   </si>
   <si>
-    <t xml:space="preserve">Sistema Ubuntu + Nginx + Node.js. NVMe = arranque y acceso ultrarrápido a archivos del sistema</t>
+    <t xml:space="preserve">Sistema Ubuntu + Nginx + PHP-FPM. NVMe = arranque y acceso ultrarrápido a archivos del sistema</t>
   </si>
   <si>
     <t xml:space="preserve">HDD 2 TB</t>
@@ -2017,7 +2017,7 @@
     <t xml:space="preserve">Intel Core i5-12400 · 6 núcleos</t>
   </si>
   <si>
-    <t xml:space="preserve">Sin GPU dedicada. 6 núcleos manejan MySQL + Node.js + Nginx simultáneamente sin cuellos de botella.</t>
+    <t xml:space="preserve">Sin GPU dedicada. 6 núcleos manejan MySQL + PHP-FPM + Nginx simultáneamente sin cuellos de botella.</t>
   </si>
   <si>
     <t xml:space="preserve">Suficiente para todo el tráfico diario de una tienda de barrio/autoservicio.</t>
@@ -2176,7 +2176,7 @@
     <t xml:space="preserve">Puerto API / Base de datos</t>
   </si>
   <si>
-    <t xml:space="preserve">3000 (Node.js) / 3306 (MySQL)</t>
+    <t xml:space="preserve">80/443 (Nginx + PHP) / 3306 (MySQL)</t>
   </si>
   <si>
     <t xml:space="preserve">Puertos internos, NUNCA expuestos fuera del servidor — solo accesibles desde localhost.</t>
@@ -2446,13 +2446,13 @@
     <t xml:space="preserve">Lenguajes</t>
   </si>
   <si>
-    <t xml:space="preserve">Node.js 20 LTS, Python 3.12</t>
+    <t xml:space="preserve">PHP 8.2, JavaScript (ES6+)</t>
   </si>
   <si>
     <t xml:space="preserve">Frameworks</t>
   </si>
   <si>
-    <t xml:space="preserve">React 18, Express, FastAPI</t>
+    <t xml:space="preserve">Laravel 11, Bootstrap 5, React Native</t>
   </si>
   <si>
     <t xml:space="preserve">Librerías</t>
